--- a/Samples/01_Illuminated_JV.xlsx
+++ b/Samples/01_Illuminated_JV.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Forward Voltage (V)</t>
   </si>
@@ -98,6 +98,18 @@
     <t>Scan Rate (mV/s)</t>
   </si>
   <si>
+    <t>Scan Order</t>
+  </si>
+  <si>
+    <t>Illumination (mW/cm²)</t>
+  </si>
+  <si>
+    <t>Detector Power (mW)</t>
+  </si>
+  <si>
+    <t>Detector Area (cm²)</t>
+  </si>
+  <si>
     <t>Simulated DummyCell SMU (sample data — not a real instrument)</t>
   </si>
   <si>
@@ -164,7 +176,7 @@
     <t>curve_fit+brentq</t>
   </si>
   <si>
-    <t>2026-06-22 16:18:44</t>
+    <t>2026-10-23 18:50:27</t>
   </si>
   <si>
     <t>none</t>
@@ -556,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA68"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="26" width="14.7109375" customWidth="1"/>
+    <col min="7" max="31" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,8 +657,20 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:27">
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="G2" s="2">
         <v>0.1</v>
       </c>
@@ -705,13 +729,16 @@
         <v>0</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AA2" s="2">
         <v>352.9411764705882</v>
       </c>
-    </row>
-    <row r="3" spans="1:27">
+      <c r="AC2" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" s="3">
         <v>-0.1</v>
       </c>
@@ -731,7 +758,7 @@
         <v>-2.362591605596222</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:31">
       <c r="A4" s="3">
         <v>-0.08</v>
       </c>
@@ -751,7 +778,7 @@
         <v>-1.889806795469509</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:31">
       <c r="A5" s="3">
         <v>-0.06</v>
       </c>
@@ -771,7 +798,7 @@
         <v>-1.417155229846455</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:31">
       <c r="A6" s="3">
         <v>-0.04</v>
       </c>
@@ -791,7 +818,7 @@
         <v>-0.9446369087270998</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:31">
       <c r="A7" s="3">
         <v>-0.02</v>
       </c>
@@ -811,7 +838,7 @@
         <v>-0.4722518321115418</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:31">
       <c r="A8" s="3">
         <v>0</v>
       </c>
@@ -831,7 +858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:31">
       <c r="A9" s="3">
         <v>0.02</v>
       </c>
@@ -851,7 +878,7 @@
         <v>0.4721185876070617</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:31">
       <c r="A10" s="3">
         <v>0.04</v>
       </c>
@@ -871,7 +898,7 @@
         <v>0.9441039307086978</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:31">
       <c r="A11" s="3">
         <v>0.06</v>
       </c>
@@ -891,7 +918,7 @@
         <v>1.415956029303031</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:31">
       <c r="A12" s="3">
         <v>0.08</v>
       </c>
@@ -911,7 +938,7 @@
         <v>1.887674883386404</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:31">
       <c r="A13" s="3">
         <v>0.1</v>
       </c>
@@ -931,7 +958,7 @@
         <v>2.359260492951801</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:31">
       <c r="A14" s="3">
         <v>0.12</v>
       </c>
@@ -951,7 +978,7 @@
         <v>2.83071285798592</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:31">
       <c r="A15" s="3">
         <v>0.14</v>
       </c>
@@ -971,7 +998,7 @@
         <v>3.30203197846378</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:31">
       <c r="A16" s="3">
         <v>0.16</v>
       </c>
@@ -2048,21 +2075,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3">
         <v>23.625</v>
@@ -2071,12 +2098,12 @@
         <v>3.982194008364882E-15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3">
         <v>1.999999999999935E-12</v>
@@ -2085,12 +2112,12 @@
         <v>2.002245255064854E-25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>1.449999999999999</v>
@@ -2099,12 +2126,12 @@
         <v>4.84048189461931E-15</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3">
         <v>4.000000000000002</v>
@@ -2113,12 +2140,12 @@
         <v>7.039920277021871E-15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>5999.999999999991</v>
@@ -2127,12 +2154,12 @@
         <v>2.647984137940508E-10</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -2141,52 +2168,52 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8" s="3">
         <v>1.356919346659807E-14</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3">
         <v>6.887342819841329E-15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3">
         <v>298.15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
